--- a/data/trans_camb/P38B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Estudios-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,12</t>
+          <t>-2,14; 4,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 4,57</t>
+          <t>-2,15; 4,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 2,54</t>
+          <t>-1,87; 2,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 3,35</t>
+          <t>-0,89; 3,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 2,31</t>
+          <t>-1,31; 2,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 3,46</t>
+          <t>-0,56; 3,41</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 4,76</t>
+          <t>-2,37; 4,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 5,29</t>
+          <t>-2,41; 5,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 2,79</t>
+          <t>-1,99; 2,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,64</t>
+          <t>-0,94; 3,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,57</t>
+          <t>-1,43; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,86</t>
+          <t>-0,59; 3,79</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 4,45</t>
+          <t>-1,16; 4,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-29,92; 1,22</t>
+          <t>-30,44; 1,36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,73</t>
+          <t>-0,94; 3,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 3,94</t>
+          <t>-9,27; 3,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 3,38</t>
+          <t>0,01; 3,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,81; 1,52</t>
+          <t>-19,59; 1,28</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 5,91</t>
+          <t>-1,43; 5,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-37,93; 1,53</t>
+          <t>-39,46; 1,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,5</t>
+          <t>-1,07; 4,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 4,65</t>
+          <t>-10,94; 4,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 4,25</t>
+          <t>0,01; 4,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 1,86</t>
+          <t>-24,29; 1,59</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,01; -1,42</t>
+          <t>-10,8; -1,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -0,05</t>
+          <t>-9,68; 0,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 1,38</t>
+          <t>-7,93; 1,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,62</t>
+          <t>-1,84; 6,38</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; -1,78</t>
+          <t>-7,98; -1,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 1,95</t>
+          <t>-4,86; 1,73</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,26; -1,81</t>
+          <t>-12,1; -2,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -0,14</t>
+          <t>-11,04; 0,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 1,52</t>
+          <t>-8,91; 1,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 7,98</t>
+          <t>-2,03; 7,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,46; -2,06</t>
+          <t>-8,94; -1,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 2,29</t>
+          <t>-5,43; 2,03</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 1,82</t>
+          <t>-2,41; 1,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-23,86; -0,31</t>
+          <t>-26,08; -0,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 1,27</t>
+          <t>-1,97; 1,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 1,41</t>
+          <t>-7,26; 1,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,84</t>
+          <t>-1,67; 0,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,89; -0,25</t>
+          <t>-13,2; -0,17</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 2,25</t>
+          <t>-2,89; 1,99</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-28,89; -0,36</t>
+          <t>-31,54; -0,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 1,46</t>
+          <t>-2,24; 1,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,1; 1,63</t>
+          <t>-8,27; 1,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 0,99</t>
+          <t>-1,95; 1,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,39; -0,29</t>
+          <t>-15,45; -0,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P38B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P38B-Estudios-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,51</t>
+          <t>-0,89</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,49</t>
+          <t>0,31</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 4,08</t>
+          <t>-2,59; 3,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 4,68</t>
+          <t>-4,64; 2,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 2,59</t>
+          <t>-1,87; 2,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,44</t>
+          <t>-0,9; 3,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 2,16</t>
+          <t>-1,58; 2,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 3,41</t>
+          <t>-1,95; 2,38</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>-1,02%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 4,7</t>
+          <t>-2,9; 4,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 5,34</t>
+          <t>-5,2; 3,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,81</t>
+          <t>-1,98; 2,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,76</t>
+          <t>-0,97; 3,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,4</t>
+          <t>-1,7; 2,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 3,79</t>
+          <t>-2,12; 2,64</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-7,98</t>
+          <t>-0,82</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,31</t>
+          <t>-0,81</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 4,29</t>
+          <t>-1,03; 4,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-30,44; 1,36</t>
+          <t>-3,83; 2,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 3,88</t>
+          <t>-0,82; 3,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 3,92</t>
+          <t>-3,56; 1,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 3,59</t>
+          <t>-0,15; 3,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 1,28</t>
+          <t>-2,77; 1,1</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>-10,27%</t>
+          <t>-1,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,99%</t>
+          <t>-1,26%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,34%</t>
+          <t>-1,0%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,67</t>
+          <t>-1,31; 5,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,46; 1,68</t>
+          <t>-4,87; 2,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,71</t>
+          <t>-0,93; 4,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 4,7</t>
+          <t>-4,19; 1,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,45</t>
+          <t>-0,2; 4,29</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,29; 1,59</t>
+          <t>-3,4; 1,37</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>-4,65</t>
+          <t>-4,01</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>2,3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-0,82</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; -1,62</t>
+          <t>-11,3; -1,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 0,03</t>
+          <t>-8,69; 0,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 1,44</t>
+          <t>-7,56; 1,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 6,38</t>
+          <t>-1,76; 6,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,98; -1,57</t>
+          <t>-8,36; -1,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 1,73</t>
+          <t>-3,82; 2,47</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>-5,29%</t>
+          <t>-4,56%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-1,46%</t>
+          <t>-0,93%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-12,1; -2,0</t>
+          <t>-12,74; -2,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 0,01</t>
+          <t>-9,62; 0,58</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 1,68</t>
+          <t>-8,48; 1,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 7,7</t>
+          <t>-1,93; 7,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -1,8</t>
+          <t>-9,39; -1,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 2,03</t>
+          <t>-4,28; 2,89</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-6,88</t>
+          <t>-2,1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,22</t>
+          <t>-1,11</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,94</t>
+          <t>-1,57</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,6</t>
+          <t>-2,13; 1,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-26,08; -0,37</t>
+          <t>-4,17; -0,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,25</t>
+          <t>-2,03; 1,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,26; 1,44</t>
+          <t>-2,78; 0,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,9</t>
+          <t>-1,46; 1,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,2; -0,17</t>
+          <t>-2,82; -0,1</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-8,38%</t>
+          <t>-2,56%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,39%</t>
+          <t>-1,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-4,64%</t>
+          <t>-1,84%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 1,99</t>
+          <t>-2,57; 1,72</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-31,54; -0,43</t>
+          <t>-5,08; -0,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,44</t>
+          <t>-2,29; 1,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 1,6</t>
+          <t>-3,13; 0,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 1,07</t>
+          <t>-1,71; 1,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-15,45; -0,19</t>
+          <t>-3,31; -0,13</t>
         </is>
       </c>
     </row>
